--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260914.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260914.xlsx
@@ -6150,19 +6150,19 @@
         </is>
       </c>
       <c r="L38" s="19" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="M38" s="20" t="n">
         <v>5</v>
       </c>
       <c r="N38" s="16" t="inlineStr">
         <is>
-          <t>**サービス別単価・見込量試算（04_算定・見込量・10シート）を作成し、算定シートの05・06に投入済み。**年報 様式2から29区分の令和3〜7年度の件数・単位数・費用額・給付費を取り出し（正規化後の合計は様式2の総計と全年度一致）、第1号被保険者1人当たりの利用率で令和9〜11年度を試算した。総給付費は3年計3,089,383千円、標準給付費は3,330,495千円（第9期見込の93.4％）。**分母の変動係数は第1号被保険者数1.63％に対し認定者数5.18％で、認定者ベースだと3年計で312,871千円（10.2％）低く出ることを定量化した**</t>
+          <t>**サービス別単価・見込量試算（04_算定・見込量・10シート）を作成し、算定シートの05・06に投入済み。**年報 様式2から29区分の令和3〜7年度の件数・単位数・費用額・給付費を取り出し（正規化後の合計は様式2の総計と全年度一致）、第1号被保険者1人当たりの利用率で令和9〜11年度を試算した。総給付費は3年計3,089,383千円、標準給付費は3,330,495千円（第9期見込の93.4％）。**分母の変動係数は第1号被保険者数1.63％に対し認定者数5.18％で、認定者ベースだと3年計で312,871千円（10.2％）低く出ることを定量化した。****さらに9月14日に受領した国保連月報のExcel版により、回数・日数ベースの見込量を組んだ（回数日数ベース見込量・7シート）。**サービス種類別×要介護度別の日数を令和6・7年度の24か月分集計し、1件当たり日数を求めて見込件数に乗じた。計画書の見込量表に載せる形まで作成済み</t>
         </is>
       </c>
       <c r="O38" s="16" t="inlineStr">
         <is>
-          <t>**回数・日数ベースの見込量は、令和8年9月14日に受領した国保連月報のExcel版（THRK0201 サービス種類別給付状況その2・日数）で組める見通しがついた。**サービス種類別×要介護度別の日数・回数が月次28か月分ある。残る前提は報酬改定率（令和9年度）の確定</t>
+          <t>**報酬改定率（令和9年度）の確定。**あわせて、訪問系を回数で載せるか日数で載せるかの判断（月報の日数は実日数で、1日当たり単位数からみて回数は日数を1割程度上回る）と、趨勢のある2サービス（訪問介護・介護予防訪問看護）の基準期間の選択</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260914.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260914.xlsx
@@ -6516,19 +6516,19 @@
         </is>
       </c>
       <c r="L43" s="19" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="M43" s="20" t="n">
         <v>5</v>
       </c>
       <c r="N43" s="16" t="inlineStr">
         <is>
-          <t>**第2版（5章＋資料編・67表・約32,000字）。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。未確定156箇所を5区分で明示</t>
+          <t>**第3版（5章＋資料編・71表）。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。**第2版の未確定180箇所のうち59箇所が解消し121箇所となった。**第2章6（被保険者数・認定者数の見込み）を第10期将来推計用推計人口で確定し、第4章③にサービス見込量（回数・日数ベース）・給付費・標準給付費・保険料基準額（月額6,682円）を入れた</t>
         </is>
       </c>
       <c r="O43" s="16" t="inlineStr">
         <is>
-          <t>見込量・保険料（P7）、成果指標の現状値（依頼票H1〜H15）</t>
+          <t>**残る121箇所の内訳は、協議会で設定する目標値38、町データ待ち33、施策の本文22、算定12、町・国の決定9、見える化出力6。町データ待ちの筆頭は地域支援事業費の事業別内訳と成果指標の現状値**</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260914.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260914.xlsx
@@ -6523,12 +6523,12 @@
       </c>
       <c r="N43" s="16" t="inlineStr">
         <is>
-          <t>**第3版（5章＋資料編・71表）。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。**第2版の未確定180箇所のうち59箇所が解消し121箇所となった。**第2章6（被保険者数・認定者数の見込み）を第10期将来推計用推計人口で確定し、第4章③にサービス見込量（回数・日数ベース）・給付費・標準給付費・保険料基準額（月額6,682円）を入れた</t>
+          <t>**第3版（5章＋資料編・73表・約37,300字）。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。**第2版の未確定158箇所のうち57箇所が解消し101箇所となった**（従来122箇所と数えていたうち22箇所は本文の見出しラベルであり、未確定箇所ではなかった。集計から除いた）。第2章6（被保険者数・認定者数の見込み）を第10期将来推計用推計人口で確定し、第4章③にサービス見込量（回数・日数ベース）・給付費・標準給付費・保険料基準額（月額6,682円）を入れた</t>
         </is>
       </c>
       <c r="O43" s="16" t="inlineStr">
         <is>
-          <t>**残る121箇所の内訳は、協議会で設定する目標値38、町データ待ち33、施策の本文22、算定12、町・国の決定9、見える化出力6。町データ待ちの筆頭は地域支援事業費の事業別内訳と成果指標の現状値**</t>
+          <t>**残る101箇所の内訳は、協議会で設定する目標値39、町データ待ち34、算定12、町・国の決定9、見える化出力6、保険料の算定1。町データ待ちの筆頭は地域支援事業費の事業別内訳と成果指標の現状値**</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260914.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260914.xlsx
@@ -147,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -197,6 +197,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1241,7 +1244,7 @@
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>**第10期（令和9〜11年度）の総給付費は3年計3,089,383千円、標準給付費は3,330,495千円で、第9期の見込み3,566,486千円の93.4％である。**この見込量で算式を通すと保険料基準額は月額6,682円（基金取崩なし）となる。第9期は6,600円であった。**ただし地域支援事業費・調整交付金・基金取崩額・第1号被保険者負担割合のいずれもが未確定であり、確定値ではない。**</t>
+          <t>**第10期（令和9〜11年度）の総給付費は3年計3,043,066千円、標準給付費は3,280,604千円で、第9期の見込み3,566,486千円の92.0％である。**この見込量に地域支援事業費（年報 様式4 の令和6年度決算・3年計191,749千円）を加えて算式を通すと、保険料基準額は月額6,558円（基金取崩なし）となる。第9期は6,600円であった。**ただし調整交付金・基金取崩額・第1号被保険者負担割合のいずれもが未確定であり、確定値ではない。**</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1850,7 @@
       <c r="E2" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="23" t="inlineStr">
+      <c r="F2" s="24" t="inlineStr">
         <is>
           <t>前提条項</t>
         </is>
@@ -1877,7 +1880,7 @@
       <c r="E3" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="23" t="inlineStr">
+      <c r="F3" s="24" t="inlineStr">
         <is>
           <t>前提条項</t>
         </is>
@@ -2641,7 +2644,7 @@
       <c r="E27" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F27" s="23" t="inlineStr">
+      <c r="F27" s="24" t="inlineStr">
         <is>
           <t>前提条項</t>
         </is>
@@ -2834,7 +2837,7 @@
         <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A2,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
-      <c r="I2" s="24">
+      <c r="I2" s="25">
         <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A2)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A2)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A2)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
@@ -2879,7 +2882,7 @@
         <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A3,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="25">
         <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A3)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A3)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A3)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
@@ -2924,7 +2927,7 @@
         <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A4,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
-      <c r="I4" s="24">
+      <c r="I4" s="25">
         <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A4)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A4)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A4)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
@@ -2969,7 +2972,7 @@
         <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A5,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
-      <c r="I5" s="24">
+      <c r="I5" s="25">
         <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A5)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A5)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A5)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
@@ -3014,7 +3017,7 @@
         <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A6,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="25">
         <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A6)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A6)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A6)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
@@ -3059,7 +3062,7 @@
         <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A7,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="25">
         <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A7)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A7)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A7)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
@@ -3104,7 +3107,7 @@
         <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A8,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="25">
         <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A8)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A8)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A8)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
@@ -3149,7 +3152,7 @@
         <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A9,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="25">
         <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A9)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A9)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A9)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
@@ -3194,7 +3197,7 @@
         <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A10,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
-      <c r="I10" s="24">
+      <c r="I10" s="25">
         <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A10)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A10)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A10)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
@@ -3239,7 +3242,7 @@
         <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A11,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
-      <c r="I11" s="24">
+      <c r="I11" s="25">
         <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A11)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A11)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A11)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
@@ -3284,7 +3287,7 @@
         <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A12,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="25">
         <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A12)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A12)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A12)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
@@ -3295,37 +3298,37 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr"/>
-      <c r="C13" s="26">
+      <c r="B13" s="26" t="inlineStr"/>
+      <c r="C13" s="27">
         <f>SUM(C2:C12)</f>
         <v/>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="27">
         <f>SUM(D2:D12)</f>
         <v/>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <f>SUM(E2:E12)</f>
         <v/>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="27">
         <f>SUM(F2:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="27">
         <f>SUM(G2:G12)</f>
         <v/>
       </c>
-      <c r="H13" s="26">
+      <c r="H13" s="27">
         <f>SUM(H2:H12)</f>
         <v/>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="28">
         <f>IF(SUM('01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT('01_WBS'!$L$2:$L$64,'01_WBS'!$M$2:$M$64)/SUM('01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
@@ -3363,7 +3366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:P64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3532,6 +3535,7 @@
           <t>―</t>
         </is>
       </c>
+      <c r="P2" s="21" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
@@ -3605,6 +3609,7 @@
           <t>―</t>
         </is>
       </c>
+      <c r="P3" s="21" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
@@ -3678,6 +3683,7 @@
           <t>―</t>
         </is>
       </c>
+      <c r="P4" s="21" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
@@ -3751,6 +3757,7 @@
           <t>―</t>
         </is>
       </c>
+      <c r="P5" s="21" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -3824,6 +3831,7 @@
           <t>―</t>
         </is>
       </c>
+      <c r="P6" s="21" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
@@ -3897,6 +3905,7 @@
           <t>―</t>
         </is>
       </c>
+      <c r="P7" s="21" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
@@ -3970,6 +3979,7 @@
           <t>残るのは地域支援事業費の内訳（S6）、令和7年度決算（S7）、成果指標の現状値17項目（H1〜H17）</t>
         </is>
       </c>
+      <c r="P8" s="21" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
@@ -4022,7 +4032,7 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K9" s="21" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
@@ -4043,6 +4053,7 @@
           <t>**町との協議。協議会の回数が決まらないとP6・P8・P9・P10の日程が引けない**</t>
         </is>
       </c>
+      <c r="P9" s="21" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
@@ -4116,6 +4127,7 @@
           <t>―</t>
         </is>
       </c>
+      <c r="P10" s="21" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
@@ -4189,6 +4201,7 @@
           <t>―</t>
         </is>
       </c>
+      <c r="P11" s="21" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
@@ -4262,6 +4275,7 @@
           <t>―</t>
         </is>
       </c>
+      <c r="P12" s="21" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
@@ -4335,6 +4349,7 @@
           <t>**「令和7年8〜9月に計上方法の変更がなかったか」に論点が絞られた。町外施設入所者の帰属、住所地特例、国保連の集計定義のいずれか**</t>
         </is>
       </c>
+      <c r="P13" s="21" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
@@ -4408,6 +4423,7 @@
           <t>―</t>
         </is>
       </c>
+      <c r="P14" s="21" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
@@ -4460,7 +4476,7 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K15" s="22" t="inlineStr">
+      <c r="K15" s="23" t="inlineStr">
         <is>
           <t>データ待ち</t>
         </is>
@@ -4481,6 +4497,7 @@
           <t>**町の事業実績（依頼票H3）。見える化の0か所と調査の5.5％が整合しない**</t>
         </is>
       </c>
+      <c r="P15" s="21" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
@@ -4555,6 +4572,7 @@
           <t>研修系（J1〜J15）は本町の値が未公表。町の実績で代替する（依頼票H9）</t>
         </is>
       </c>
+      <c r="P16" s="21" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
@@ -4628,6 +4646,7 @@
           <t>―</t>
         </is>
       </c>
+      <c r="P17" s="21" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
@@ -4701,6 +4720,7 @@
           <t>**令和7年度の様式4が全て0で未入力。また基金保有額が令和4年度末120百万円から令和5年度末12百万円へ1桁減っており、取崩実績か入力誤りかの確認が要る**</t>
         </is>
       </c>
+      <c r="P18" s="21" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
@@ -4753,7 +4773,7 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K19" s="23" t="inlineStr">
+      <c r="K19" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -4774,6 +4794,7 @@
           <t>見える化システムへのアクセス</t>
         </is>
       </c>
+      <c r="P19" s="21" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
@@ -4848,6 +4869,7 @@
           <t>町の給付実績（依頼票S1・S2）で数値を確定する</t>
         </is>
       </c>
+      <c r="P20" s="21" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
@@ -4921,6 +4943,7 @@
           <t>見える化システムの値との突合作業</t>
         </is>
       </c>
+      <c r="P21" s="21" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
@@ -4973,7 +4996,7 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="K22" s="23" t="inlineStr">
+      <c r="K22" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -4994,6 +5017,7 @@
           <t>報告書の確定</t>
         </is>
       </c>
+      <c r="P22" s="21" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
@@ -5067,6 +5091,7 @@
           <t>―</t>
         </is>
       </c>
+      <c r="P23" s="21" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
@@ -5140,6 +5165,7 @@
           <t>―</t>
         </is>
       </c>
+      <c r="P24" s="21" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
@@ -5213,6 +5239,7 @@
           <t>―</t>
         </is>
       </c>
+      <c r="P25" s="21" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
@@ -5286,6 +5313,7 @@
           <t>―</t>
         </is>
       </c>
+      <c r="P26" s="21" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
@@ -5338,7 +5366,7 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K27" s="22" t="inlineStr">
+      <c r="K27" s="23" t="inlineStr">
         <is>
           <t>データ待ち</t>
         </is>
@@ -5359,6 +5387,7 @@
           <t>**令和7年度調査の個票データ（依頼票H16）。地区情報の有無も要確認**</t>
         </is>
       </c>
+      <c r="P27" s="21" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
@@ -5432,6 +5461,7 @@
           <t>―</t>
         </is>
       </c>
+      <c r="P28" s="21" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
@@ -5506,6 +5536,7 @@
           <t>―</t>
         </is>
       </c>
+      <c r="P29" s="21" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
@@ -5579,6 +5610,7 @@
           <t>**地域支援事業費の実績（年報 様式4の令和6・7年度が未入力。依頼票H3）と成果指標の現状値（H1〜H15）。令和8年度は年度途中のため令和9年夏の年報を待つ**</t>
         </is>
       </c>
+      <c r="P30" s="21" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
@@ -5631,7 +5663,7 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K31" s="23" t="inlineStr">
+      <c r="K31" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -5652,6 +5684,7 @@
           <t>整備の経緯の確認（依頼票H15）</t>
         </is>
       </c>
+      <c r="P31" s="21" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
@@ -5726,6 +5759,7 @@
           <t>実績データによる数値の確定</t>
         </is>
       </c>
+      <c r="P32" s="21" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
@@ -5779,7 +5813,7 @@
           <t>2026-11</t>
         </is>
       </c>
-      <c r="K33" s="23" t="inlineStr">
+      <c r="K33" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -5800,6 +5834,7 @@
           <t>**協議会の開催回数・時期が未定（依頼票C4）**</t>
         </is>
       </c>
+      <c r="P33" s="21" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
@@ -5852,7 +5887,7 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="K34" s="23" t="inlineStr">
+      <c r="K34" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -5873,6 +5908,7 @@
           <t>骨子案の確定</t>
         </is>
       </c>
+      <c r="P34" s="21" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
@@ -5946,6 +5982,7 @@
           <t>―</t>
         </is>
       </c>
+      <c r="P35" s="21" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
@@ -6019,6 +6056,7 @@
           <t>―</t>
         </is>
       </c>
+      <c r="P36" s="21" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
@@ -6092,6 +6130,7 @@
           <t>**認定率をどの水準で置くか（令和7年度実績か、計上変更前の令和6年度水準か）。2-4の確認結果しだいで前提が変わる**</t>
         </is>
       </c>
+      <c r="P37" s="21" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
@@ -6157,12 +6196,17 @@
       </c>
       <c r="N38" s="16" t="inlineStr">
         <is>
-          <t>**サービス別単価・見込量試算（04_算定・見込量・10シート）を作成し、算定シートの05・06に投入済み。**年報 様式2から29区分の令和3〜7年度の件数・単位数・費用額・給付費を取り出し（正規化後の合計は様式2の総計と全年度一致）、第1号被保険者1人当たりの利用率で令和9〜11年度を試算した。総給付費は3年計3,089,383千円、標準給付費は3,330,495千円（第9期見込の93.4％）。**分母の変動係数は第1号被保険者数1.63％に対し認定者数5.18％で、認定者ベースだと3年計で312,871千円（10.2％）低く出ることを定量化した。****さらに9月14日に受領した国保連月報のExcel版により、回数・日数ベースの見込量を組んだ（回数日数ベース見込量・7シート）。**サービス種類別×要介護度別の日数を令和6・7年度の24か月分集計し、1件当たり日数を求めて見込件数に乗じた。計画書の見込量表に載せる形まで作成済み</t>
+          <t>**サービス別単価・見込量試算（04_算定・見込量・10シート）を作成し、算定シートの05・06に投入済み。**年報 様式2から29区分の令和3〜7年度の件数・単位数・費用額・給付費を取り出し（正規化後の合計は様式2の総計と全年度一致）、第1号被保険者1人当たりの利用率で令和9〜11年度を試算した。総給付費は3年計3,043,066千円、標準給付費は3,280,604千円（第9期見込の92.0％）。**分母の変動係数は第1号被保険者数1.63％に対し認定者数5.18％で、認定者ベースだと3年計で312,871千円（10.2％）低く出ることを定量化した。****さらに9月14日に受領した国保連月報のExcel版により、回数・日数ベースの見込量を組んだ（回数日数ベース見込量・7シート）。**サービス種類別×要介護度別の日数を令和6・7年度の24か月分集計し、1件当たり日数を求めて見込件数に乗じた。計画書の見込量表に載せる形まで作成済み</t>
         </is>
       </c>
       <c r="O38" s="16" t="inlineStr">
         <is>
-          <t>**報酬改定率（令和9年度）の確定。**あわせて、訪問系を回数で載せるか日数で載せるかの判断（月報の日数は実日数で、1日当たり単位数からみて回数は日数を1割程度上回る）と、趨勢のある2サービス（訪問介護・介護予防訪問看護）の基準期間の選択</t>
+          <t>**9月14日に受領した見える化のワークシート（将来推計1）と突き合わせ、3サービスの基準期間を令和7年度単年に改めた**（認知症対応型共同生活介護・介護予防認知症対応型共同生活介護・介護予防福祉用具貸与）。令和5→7年度が単調で、令和8年度の月報も同じ向きに続いており、3年平均が直近実績と10％以上離れていたもの。総給付費は3年計で46,317千円（1.5％）下がった</t>
+        </is>
+      </c>
+      <c r="P38" s="17" t="inlineStr">
+        <is>
+          <t>**報酬改定率（令和9年度）の確定。**あわせて、通所リハビリテーションの令和8年度の状況（見える化は令和7年度の2.65倍だが月報は横ばい）と、短期入所生活介護の増加（月報で令和8年度＋29％）の理由の確認</t>
         </is>
       </c>
     </row>
@@ -6217,7 +6261,7 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K39" s="21" t="inlineStr">
+      <c r="K39" s="22" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
@@ -6238,6 +6282,7 @@
           <t>**アカウント・権限・作業範囲・時期の確認（依頼票C5）。これが決まらないと総括表が出せず、対計画比・供給実現性の検証に進めない**</t>
         </is>
       </c>
+      <c r="P39" s="21" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
@@ -6303,14 +6348,15 @@
       </c>
       <c r="N40" s="16" t="inlineStr">
         <is>
-          <t>**所得段階別被保険者数（13段階）、小野町が定める保険料率（第1〜3段階は0.285／0.486／0.685で国の標準より低い）、収納率99.35％、基金保有額12,000千円を投入済み。**7-4の見込量で算式を通したところ、保険料基準額は月額6,682円（基金取崩なし）、6,580円（保有額12,000千円を全額取崩）、6,383円（第9期と同じ35,000千円を取崩）となった。第9期は6,600円。**調整交付金の見込交付割合は第9期計画の公表値から逆算して5.963％。標準の5％ではない（小野町は後期高齢者加入割合が高く低所得層が厚い）**</t>
+          <t>**所得段階別被保険者数（13段階）、小野町が定める保険料率（第1〜3段階は0.285／0.486／0.685で国の標準より低い）、収納率99.35％、基金保有額12,000千円を投入済み。地域支援事業費は年報 様式4 の令和6年度決算63,916千円（3年計191,749千円）を置いた。**7-4の見込量で算式を通したところ、保険料基準額は月額6,558円（基金取崩なし）、6,456円（保有額12,000千円を全額取崩）、6,259円（第9期と同じ35,000千円を取崩）となった。第9期は6,600円。負担割合が24％になると6,856円。**調整交付金の見込交付割合は第9期計画の公表値から逆算して5.963％。標準の5％ではない（小野町は後期高齢者加入割合が高く低所得層が厚い）**</t>
         </is>
       </c>
       <c r="O40" s="16" t="inlineStr">
         <is>
-          <t>**地域支援事業費の実績（年報 様式4が未入力）、調整交付金見込額、第10期の第1号被保険者負担割合。あわせて、第9期が見込んだ基金取崩35,000千円に対し基金保有額が12,000千円しかない点の確認が要る**</t>
-        </is>
-      </c>
+          <t>**地域支援事業費の事業別内訳（年報 様式4 は3科目の合計しか持たない）、令和7年度の決算額（年報が未入力）、調整交付金見込額、第10期の第1号被保険者負担割合。あわせて、第9期が見込んだ基金取崩35,000千円に対し基金保有額が12,000千円しかない点の確認が要る**</t>
+        </is>
+      </c>
+      <c r="P40" s="21" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
@@ -6363,7 +6409,7 @@
           <t>2026-12</t>
         </is>
       </c>
-      <c r="K41" s="23" t="inlineStr">
+      <c r="K41" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -6384,6 +6430,7 @@
           <t>見込量・保険料の算定</t>
         </is>
       </c>
+      <c r="P41" s="21" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
@@ -6436,7 +6483,7 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="K42" s="23" t="inlineStr">
+      <c r="K42" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -6457,6 +6504,7 @@
           <t>報告書の確定</t>
         </is>
       </c>
+      <c r="P42" s="21" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
@@ -6523,7 +6571,7 @@
       </c>
       <c r="N43" s="16" t="inlineStr">
         <is>
-          <t>**第3版（5章＋資料編・73表・約37,300字）。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。**第2版の未確定158箇所のうち57箇所が解消し101箇所となった**（従来122箇所と数えていたうち22箇所は本文の見出しラベルであり、未確定箇所ではなかった。集計から除いた）。第2章6（被保険者数・認定者数の見込み）を第10期将来推計用推計人口で確定し、第4章③にサービス見込量（回数・日数ベース）・給付費・標準給付費・保険料基準額（月額6,682円）を入れた</t>
+          <t>**第3版（5章＋資料編・73表・約37,300字）。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。**第2版の未確定158箇所のうち57箇所が解消し101箇所となった**（従来122箇所と数えていたうち22箇所は本文の見出しラベルであり、未確定箇所ではなかった。集計から除いた）。第2章6（被保険者数・認定者数の見込み）を第10期将来推計用推計人口で確定し、第4章③にサービス見込量（回数・日数ベース）・給付費・標準給付費・保険料基準額（月額6,558円）を入れた</t>
         </is>
       </c>
       <c r="O43" s="16" t="inlineStr">
@@ -6531,6 +6579,7 @@
           <t>**残る101箇所の内訳は、協議会で設定する目標値39、町データ待ち34、算定12、町・国の決定9、見える化出力6、保険料の算定1。町データ待ちの筆頭は地域支援事業費の事業別内訳と成果指標の現状値**</t>
         </is>
       </c>
+      <c r="P43" s="21" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
@@ -6604,6 +6653,7 @@
           <t>―</t>
         </is>
       </c>
+      <c r="P44" s="21" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
@@ -6677,6 +6727,7 @@
           <t>町の意思決定（方式A／B）</t>
         </is>
       </c>
+      <c r="P45" s="21" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
@@ -6729,7 +6780,7 @@
           <t>2026-12</t>
         </is>
       </c>
-      <c r="K46" s="23" t="inlineStr">
+      <c r="K46" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -6750,6 +6801,7 @@
           <t>**P7の完了、町データの受領**</t>
         </is>
       </c>
+      <c r="P46" s="21" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
@@ -6803,7 +6855,7 @@
           <t>2026-12</t>
         </is>
       </c>
-      <c r="K47" s="23" t="inlineStr">
+      <c r="K47" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -6824,6 +6876,7 @@
           <t>協議会の開催時期</t>
         </is>
       </c>
+      <c r="P47" s="21" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
@@ -6876,7 +6929,7 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="K48" s="23" t="inlineStr">
+      <c r="K48" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -6897,6 +6950,7 @@
           <t>素案の確定</t>
         </is>
       </c>
+      <c r="P48" s="21" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
@@ -6949,7 +7003,7 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K49" s="21" t="inlineStr">
+      <c r="K49" s="22" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
@@ -6970,6 +7024,7 @@
           <t>**町との協議（依頼票C4）。これが決まらないと工程が引けない**</t>
         </is>
       </c>
+      <c r="P49" s="21" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
@@ -7022,7 +7077,7 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K50" s="21" t="inlineStr">
+      <c r="K50" s="22" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
@@ -7043,6 +7098,7 @@
           <t>**開催日が未定**</t>
         </is>
       </c>
+      <c r="P50" s="21" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
@@ -7095,7 +7151,7 @@
           <t>2026-11</t>
         </is>
       </c>
-      <c r="K51" s="23" t="inlineStr">
+      <c r="K51" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -7116,6 +7172,7 @@
           <t>P7の完了、開催日の確定</t>
         </is>
       </c>
+      <c r="P51" s="21" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
@@ -7168,7 +7225,7 @@
           <t>2026-12</t>
         </is>
       </c>
-      <c r="K52" s="23" t="inlineStr">
+      <c r="K52" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -7189,6 +7246,7 @@
           <t>素案の確定</t>
         </is>
       </c>
+      <c r="P52" s="21" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
@@ -7262,6 +7320,7 @@
           <t>―</t>
         </is>
       </c>
+      <c r="P53" s="21" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
@@ -7314,7 +7373,7 @@
           <t>2027-01</t>
         </is>
       </c>
-      <c r="K54" s="23" t="inlineStr">
+      <c r="K54" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -7335,6 +7394,7 @@
           <t>素案の確定、実施時期の確定（依頼票C6）</t>
         </is>
       </c>
+      <c r="P54" s="21" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
@@ -7387,7 +7447,7 @@
           <t>2027-02</t>
         </is>
       </c>
-      <c r="K55" s="23" t="inlineStr">
+      <c r="K55" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -7408,6 +7468,7 @@
           <t>パブコメの実施</t>
         </is>
       </c>
+      <c r="P55" s="21" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
@@ -7460,7 +7521,7 @@
           <t>2027-02</t>
         </is>
       </c>
-      <c r="K56" s="23" t="inlineStr">
+      <c r="K56" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -7481,6 +7542,7 @@
           <t>意見への対応</t>
         </is>
       </c>
+      <c r="P56" s="21" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
@@ -7533,7 +7595,7 @@
           <t>2027-02</t>
         </is>
       </c>
-      <c r="K57" s="23" t="inlineStr">
+      <c r="K57" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -7554,6 +7616,7 @@
           <t>意見への対応</t>
         </is>
       </c>
+      <c r="P57" s="21" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
@@ -7606,7 +7669,7 @@
           <t>2027-02</t>
         </is>
       </c>
-      <c r="K58" s="23" t="inlineStr">
+      <c r="K58" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -7627,6 +7690,7 @@
           <t>原稿の確定</t>
         </is>
       </c>
+      <c r="P58" s="21" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
@@ -7679,7 +7743,7 @@
           <t>2027-02</t>
         </is>
       </c>
-      <c r="K59" s="23" t="inlineStr">
+      <c r="K59" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -7700,6 +7764,7 @@
           <t>組版</t>
         </is>
       </c>
+      <c r="P59" s="21" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
@@ -7773,6 +7838,7 @@
           <t>―</t>
         </is>
       </c>
+      <c r="P60" s="21" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
@@ -7825,7 +7891,7 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="K61" s="23" t="inlineStr">
+      <c r="K61" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -7846,6 +7912,7 @@
           <t>計画書の確定</t>
         </is>
       </c>
+      <c r="P61" s="21" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
@@ -7899,7 +7966,7 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="K62" s="23" t="inlineStr">
+      <c r="K62" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -7920,6 +7987,7 @@
           <t>校了</t>
         </is>
       </c>
+      <c r="P62" s="21" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
@@ -7972,7 +8040,7 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="K63" s="23" t="inlineStr">
+      <c r="K63" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -7993,6 +8061,7 @@
           <t>各成果品の確定</t>
         </is>
       </c>
+      <c r="P63" s="21" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
@@ -8045,7 +8114,7 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="K64" s="23" t="inlineStr">
+      <c r="K64" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -8066,6 +8135,7 @@
           <t>全成果品の完成</t>
         </is>
       </c>
+      <c r="P64" s="21" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O64"/>
@@ -8199,7 +8269,7 @@
         <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A2,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
-      <c r="H2" s="24">
+      <c r="H2" s="25">
         <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A2)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A2)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A2)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
@@ -8249,7 +8319,7 @@
         <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A3,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
-      <c r="H3" s="24">
+      <c r="H3" s="25">
         <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A3)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A3)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A3)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
@@ -8299,7 +8369,7 @@
         <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A4,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
-      <c r="H4" s="24">
+      <c r="H4" s="25">
         <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A4)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A4)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A4)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
@@ -8349,7 +8419,7 @@
         <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A5,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="25">
         <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A5)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A5)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A5)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
@@ -8399,7 +8469,7 @@
         <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A6,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="25">
         <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A6)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A6)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A6)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
@@ -8449,7 +8519,7 @@
         <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A7,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="25">
         <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A7)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A7)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A7)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
@@ -8499,7 +8569,7 @@
         <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A8,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="25">
         <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A8)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A8)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A8)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
@@ -8549,7 +8619,7 @@
         <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A9,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="25">
         <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A9)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A9)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A9)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
@@ -8599,7 +8669,7 @@
         <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A10,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="25">
         <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A10)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A10)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A10)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
@@ -8649,7 +8719,7 @@
         <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A11,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="25">
         <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A11)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A11)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A11)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
@@ -8670,36 +8740,36 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="27">
         <f>SUM(B2:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="27">
         <f>SUM(C2:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <f>SUM(D2:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <f>SUM(E2:E11)</f>
         <v/>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="27">
         <f>SUM(F2:F11)</f>
         <v/>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="27">
         <f>SUM(G2:G11)</f>
         <v/>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="28">
         <f>IF(SUM('01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT('01_WBS'!$L$2:$L$64,'01_WBS'!$M$2:$M$64)/SUM('01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
@@ -8983,7 +9053,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -9023,7 +9093,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -9113,7 +9183,7 @@
           <t>受託者</t>
         </is>
       </c>
-      <c r="D2" s="21" t="inlineStr">
+      <c r="D2" s="22" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
@@ -9140,7 +9210,7 @@
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="D3" s="21" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
@@ -9167,7 +9237,7 @@
           <t>受託者</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -9194,7 +9264,7 @@
           <t>受託者</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -9221,7 +9291,7 @@
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -9248,7 +9318,7 @@
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -9275,7 +9345,7 @@
           <t>町</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -9302,7 +9372,7 @@
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -9329,7 +9399,7 @@
           <t>受託者</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -9666,7 +9736,7 @@
           <t>見える化システム</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -9826,7 +9896,7 @@
           <t>町</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
@@ -9922,7 +9992,7 @@
           <t>町</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
@@ -9954,7 +10024,7 @@
           <t>町</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -10148,7 +10218,7 @@
           <t>パブリックコメントの結果、計画最終案</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -10301,7 +10371,7 @@
           <t>**令和7年8〜9月の計上方法の変更を町に確認する。見込量は認定者数ベースではなく受給者数・給付費の実績を基礎に組む**</t>
         </is>
       </c>
-      <c r="F2" s="21" t="inlineStr">
+      <c r="F2" s="22" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
@@ -10361,7 +10431,7 @@
           <t>受託者案（4回）を提示して町と確定する（依頼票C4）</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="22" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
@@ -10391,7 +10461,7 @@
           <t>町の事業実績（令和3〜7年度）で代替する（依頼票H3）</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>データ待ち</t>
         </is>
@@ -10473,7 +10543,7 @@
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>**基金が12百万円しかなければ35百万円の取崩は実行できない。**見込量の試算で算式を通すと、保険料基準額は取崩なしで月額6,682円、保有額12百万円を全額取り崩して6,580円、第9期と同じ35百万円で6,383円となる（第9期は6,600円）。**基金の扱いだけで月額300円動く**</t>
+          <t>**基金が12百万円しかなければ35百万円の取崩は実行できない。しかも繰入金（取崩し）は令和3〜6年度とも0円で、残高だけが1桁減っており、年報の系列自体に矛盾がある。**見込量の試算で算式を通すと、保険料基準額は取崩なしで月額6,558円、保有額12百万円を全額取り崩して6,456円、第9期と同じ35百万円で6,259円となる（第9期は6,600円）。**基金の扱いだけで月額300円動く**</t>
         </is>
       </c>
       <c r="E8" s="16" t="inlineStr">
@@ -10481,7 +10551,7 @@
           <t>取崩実績か入力誤りかを町に確認したうえで、余剰の還元（据置・引下げ・繰越金の基金積立）をケースC5・C6として算定する</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
@@ -10511,7 +10581,7 @@
           <t>整備の経緯を町に確認する（依頼票H15）</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="24" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -10710,7 +10780,7 @@
           <t>仕様書3</t>
         </is>
       </c>
-      <c r="E2" s="21" t="inlineStr">
+      <c r="E2" s="22" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
@@ -10740,7 +10810,7 @@
           <t>仕様書4(5)</t>
         </is>
       </c>
-      <c r="E3" s="21" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
@@ -10830,7 +10900,7 @@
           <t>仕様書8①（受託者が作成し相互確認）</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
